--- a/daily_matches/job_matches_2026-09-07.xlsx
+++ b/daily_matches/job_matches_2026-09-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Full-Stack Engineer - Albany</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rocket Science Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc87863da4f376</t>
+          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer - Mid Career</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, ChromaDB, Kubernetes, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8374017f54f2d04d</t>
+          <t>https://www.indeed.com/viewjob?jk=83f3d0c20a7e71fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer III - Network Perimeter &amp; CDN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9466a2d2eb017b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern - MN, CO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Xcel Energy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fedf82d7085a87b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-07.xlsx
+++ b/daily_matches/job_matches_2026-09-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=65dc6fa390e72ae6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, NoSQL, Tableau</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f3d0c20a7e71fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0d15bd8d2dcde66c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III - Network Perimeter &amp; CDN</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BLH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9466a2d2eb017b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f480c971153328b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist Intern - MN, CO</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Docker, CI/CD, Git, Databricks, Power BI, Python, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2904ed9d96d7c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Qodo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, PyTorch, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fedf82d7085a87b</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233fd9ef54a6243</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-07.xlsx
+++ b/daily_matches/job_matches_2026-09-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Ai Engineers</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Navisoft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65dc6fa390e72ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d403900cf9f48d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Stream</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,112 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d15bd8d2dcde66c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AI Specialist</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BLH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bowie, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f480c971153328b</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior AI Developer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Docker, CI/CD, Git, Databricks, Power BI, Python, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2904ed9d96d7c41</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Qodo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5233fd9ef54a6243</t>
+          <t>https://www.indeed.com/viewjob?jk=3bddb4afe7c4caf5</t>
         </is>
       </c>
     </row>
